--- a/xlsx/Power/p16.xlsx
+++ b/xlsx/Power/p16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931EAAAB-76A3-4249-94DB-8A1B1CD6DE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D847C93-B75E-48EC-BF7D-6C2FBD0365A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.20100000000000001</v>
       </c>
       <c r="C1">
-        <v>0.39600000000000002</v>
+        <v>1E-3</v>
       </c>
       <c r="D1">
-        <v>0.60399999999999998</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="E1">
-        <v>0.72299999999999998</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="F1">
-        <v>0.86199999999999999</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G1">
-        <v>0.93200000000000005</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="H1">
-        <v>0.96499999999999997</v>
+        <v>0.878</v>
       </c>
       <c r="I1">
-        <v>0.98399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="J1">
-        <v>0.998</v>
+        <v>0.97899999999999998</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="C2">
-        <v>0.16700000000000001</v>
+        <v>1E-3</v>
       </c>
       <c r="D2">
-        <v>0.29899999999999999</v>
+        <v>1.2E-2</v>
       </c>
       <c r="E2">
-        <v>0.44900000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F2">
-        <v>0.626</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="G2">
-        <v>0.75700000000000001</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="H2">
-        <v>0.879</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="I2">
-        <v>0.92500000000000004</v>
+        <v>0.77</v>
       </c>
       <c r="J2">
-        <v>0.96699999999999997</v>
+        <v>0.88500000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="C3">
-        <v>0.29699999999999999</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="D3">
-        <v>0.46300000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="E3">
-        <v>0.54200000000000004</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="F3">
-        <v>0.69499999999999995</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="G3">
         <v>0.78500000000000003</v>
       </c>
       <c r="H3">
-        <v>0.879</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="I3">
         <v>0.90800000000000003</v>
       </c>
       <c r="J3">
-        <v>0.94899999999999995</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>8.4000000000000005E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="B4">
-        <v>0.14299999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="C4">
-        <v>0.224</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="D4">
-        <v>0.32200000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="E4">
         <v>0.42</v>
       </c>
       <c r="F4">
-        <v>0.55400000000000005</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G4">
         <v>0.60699999999999998</v>
       </c>
       <c r="H4">
-        <v>0.73399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I4">
         <v>0.77700000000000002</v>
       </c>
       <c r="J4">
-        <v>0.83</v>
+        <v>0.83799999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>2E-3</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="D6">
-        <v>1E-3</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="E6">
-        <v>1.0999999999999999E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="F6">
-        <v>6.7000000000000004E-2</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="G6">
-        <v>0.185</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="H6">
-        <v>0.41199999999999998</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="I6">
-        <v>0.60799999999999998</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="J6">
-        <v>0.72399999999999998</v>
+        <v>0.78700000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,19 +596,19 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="C7">
-        <v>0.36899999999999999</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="D7">
-        <v>0.622</v>
+        <v>0.621</v>
       </c>
       <c r="E7">
-        <v>0.75600000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="F7">
-        <v>0.90400000000000003</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="G7">
-        <v>0.95099999999999996</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="H7">
         <v>0.97499999999999998</v>
@@ -628,28 +628,28 @@
         <v>0.377</v>
       </c>
       <c r="C8">
-        <v>0.58599999999999997</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="E8">
-        <v>0.82799999999999996</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F8">
-        <v>0.89200000000000002</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="G8">
-        <v>0.93200000000000005</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="H8">
-        <v>0.96699999999999997</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="I8">
-        <v>0.98899999999999999</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="J8">
-        <v>0.999</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>1E-3</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="D9">
-        <v>0.01</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="E9">
-        <v>0.124</v>
+        <v>0.754</v>
       </c>
       <c r="F9">
-        <v>0.26900000000000002</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="G9">
-        <v>0.379</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="H9">
-        <v>0.51700000000000002</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="I9">
-        <v>0.59599999999999997</v>
+        <v>0.627</v>
       </c>
       <c r="J9">
-        <v>0.63700000000000001</v>
+        <v>0.66200000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p16.xlsx
+++ b/xlsx/Power/p16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D847C93-B75E-48EC-BF7D-6C2FBD0365A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF4A33C-95AC-4C4C-AAD0-E8E27A62BD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.20100000000000001</v>
       </c>
       <c r="C1">
-        <v>1E-3</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="D1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="E1">
-        <v>0.22700000000000001</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="F1">
-        <v>0.47499999999999998</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="G1">
-        <v>0.69699999999999995</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H1">
-        <v>0.878</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="I1">
-        <v>0.94</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="J1">
-        <v>0.97899999999999998</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="C2">
-        <v>1E-3</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="D2">
-        <v>1.2E-2</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="E2">
-        <v>0.08</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="F2">
-        <v>0.23899999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="G2">
-        <v>0.39900000000000002</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="H2">
-        <v>0.64800000000000002</v>
+        <v>0.879</v>
       </c>
       <c r="I2">
-        <v>0.77</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="J2">
-        <v>0.88500000000000001</v>
+        <v>0.96699999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="C3">
-        <v>0.35899999999999999</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="D3">
-        <v>0.48</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="E3">
-        <v>0.55600000000000005</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F3">
-        <v>0.70399999999999996</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="G3">
         <v>0.78500000000000003</v>
       </c>
       <c r="H3">
-        <v>0.88300000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="I3">
         <v>0.90800000000000003</v>
       </c>
       <c r="J3">
-        <v>0.95</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9.8000000000000004E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="B4">
-        <v>0.153</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.23100000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="D4">
-        <v>0.317</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="E4">
         <v>0.42</v>
       </c>
       <c r="F4">
-        <v>0.56000000000000005</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="G4">
         <v>0.60699999999999998</v>
       </c>
       <c r="H4">
-        <v>0.73</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="I4">
         <v>0.77700000000000002</v>
       </c>
       <c r="J4">
-        <v>0.83799999999999997</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>0.19800000000000001</v>
+        <v>2E-3</v>
       </c>
       <c r="D6">
-        <v>4.9000000000000002E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="E6">
-        <v>6.3E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="F6">
-        <v>0.13100000000000001</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="G6">
-        <v>0.22800000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="H6">
-        <v>0.47199999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="I6">
-        <v>0.65400000000000003</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="J6">
-        <v>0.78700000000000003</v>
+        <v>0.72399999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,19 +596,19 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="C7">
-        <v>0.35899999999999999</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="D7">
-        <v>0.621</v>
+        <v>0.622</v>
       </c>
       <c r="E7">
-        <v>0.75900000000000001</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="F7">
-        <v>0.90300000000000002</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="G7">
-        <v>0.94699999999999995</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="H7">
         <v>0.97499999999999998</v>
@@ -628,28 +628,28 @@
         <v>0.377</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="D8">
-        <v>0.22500000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E8">
-        <v>0.47499999999999998</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="F8">
-        <v>0.67500000000000004</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="G8">
-        <v>0.82299999999999995</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H8">
-        <v>0.91300000000000003</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="I8">
-        <v>0.79800000000000004</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="J8">
-        <v>0.878</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="C9">
-        <v>5.8999999999999997E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="D9">
-        <v>0.49299999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="E9">
-        <v>0.754</v>
+        <v>0.124</v>
       </c>
       <c r="F9">
-        <v>0.47799999999999998</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="G9">
-        <v>0.48599999999999999</v>
+        <v>0.379</v>
       </c>
       <c r="H9">
-        <v>0.59699999999999998</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="I9">
-        <v>0.627</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="J9">
-        <v>0.66200000000000003</v>
+        <v>0.63700000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p16.xlsx
+++ b/xlsx/Power/p16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF4A33C-95AC-4C4C-AAD0-E8E27A62BD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C26F66-386C-4EFC-A789-3DA4CA9F5D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{128521C4-5FBC-466D-B18C-02AFBB947670}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>9.1999999999999998E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="B1">
-        <v>0.20100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="C1">
-        <v>0.39600000000000002</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="D1">
-        <v>0.60399999999999998</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="E1">
-        <v>0.72299999999999998</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="F1">
         <v>0.86199999999999999</v>
@@ -422,7 +422,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="I1">
-        <v>0.98399999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="J1">
         <v>0.998</v>
@@ -430,130 +430,130 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.05</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="B2">
-        <v>7.0999999999999994E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="C2">
-        <v>0.16700000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="D2">
-        <v>0.29899999999999999</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="E2">
-        <v>0.44900000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="F2">
-        <v>0.626</v>
+        <v>0.62</v>
       </c>
       <c r="G2">
-        <v>0.75700000000000001</v>
+        <v>0.749</v>
       </c>
       <c r="H2">
-        <v>0.879</v>
+        <v>0.878</v>
       </c>
       <c r="I2">
-        <v>0.92500000000000004</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="J2">
-        <v>0.96699999999999997</v>
+        <v>0.96899999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>8.8999999999999996E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="B3">
-        <v>0.17699999999999999</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="C3">
-        <v>0.29699999999999999</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="D3">
-        <v>0.46300000000000002</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="E3">
-        <v>0.54200000000000004</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="F3">
-        <v>0.69499999999999995</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="G3">
-        <v>0.78500000000000003</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="H3">
-        <v>0.879</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="I3">
-        <v>0.90800000000000003</v>
+        <v>0.91</v>
       </c>
       <c r="J3">
-        <v>0.94899999999999995</v>
+        <v>0.95299999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>8.4000000000000005E-2</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="B4">
-        <v>0.14299999999999999</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="C4">
-        <v>0.224</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="D4">
-        <v>0.32200000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="E4">
-        <v>0.42</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F4">
-        <v>0.55400000000000005</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="G4">
-        <v>0.60699999999999998</v>
+        <v>0.61</v>
       </c>
       <c r="H4">
-        <v>0.73399999999999999</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="I4">
-        <v>0.77700000000000002</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="J4">
-        <v>0.83</v>
+        <v>0.84499999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2E-3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2E-3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2E-3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>1.2999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -570,36 +570,36 @@
         <v>1E-3</v>
       </c>
       <c r="E6">
-        <v>1.0999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="F6">
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G6">
-        <v>0.185</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H6">
-        <v>0.41199999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="I6">
-        <v>0.60799999999999998</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J6">
-        <v>0.72399999999999998</v>
+        <v>0.74099999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2.8000000000000001E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="B7">
-        <v>0.14099999999999999</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="C7">
-        <v>0.36899999999999999</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="D7">
-        <v>0.622</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="E7">
         <v>0.75600000000000001</v>
@@ -625,19 +625,19 @@
         <v>0.156</v>
       </c>
       <c r="B8">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="C8">
-        <v>0.58599999999999997</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="E8">
-        <v>0.82799999999999996</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="F8">
-        <v>0.89200000000000002</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G8">
         <v>0.93200000000000005</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4.3999999999999997E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="B9">
-        <v>2.5999999999999999E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="C9">
         <v>1E-3</v>
       </c>
       <c r="D9">
-        <v>0.01</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E9">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="F9">
-        <v>0.26900000000000002</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="G9">
-        <v>0.379</v>
+        <v>0.373</v>
       </c>
       <c r="H9">
-        <v>0.51700000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="I9">
-        <v>0.59599999999999997</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="J9">
-        <v>0.63700000000000001</v>
+        <v>0.64100000000000001</v>
       </c>
     </row>
   </sheetData>
